--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104644_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104644_W21.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5802</v>
+        <v>9.982799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7221</v>
+        <v>8.2469</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8581</v>
+        <v>1.7359</v>
       </c>
       <c r="G2" t="n">
-        <v>8.9838</v>
+        <v>8.9686</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4992</v>
+        <v>1.5019</v>
       </c>
       <c r="I2" t="n">
-        <v>7.4847</v>
+        <v>7.4666</v>
       </c>
       <c r="J2" t="n">
-        <v>8.182700000000001</v>
+        <v>8.1334</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0363</v>
+        <v>2.02</v>
       </c>
       <c r="L2" t="n">
-        <v>6.1464</v>
+        <v>6.1134</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8011</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3382</v>
+        <v>1.3532</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1618</v>
+        <v>0.2709</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3115</v>
+        <v>0.2808</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1497</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1173</v>
+        <v>6.1304</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4204</v>
+        <v>5.6893</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6969</v>
+        <v>0.441</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4669</v>
+        <v>4.458</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0924</v>
+        <v>1.0887</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3745</v>
+        <v>3.3693</v>
       </c>
       <c r="J3" t="n">
-        <v>4.914</v>
+        <v>4.8837</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4014</v>
+        <v>0.3857</v>
       </c>
       <c r="L3" t="n">
-        <v>4.5126</v>
+        <v>4.498</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4471</v>
+        <v>-0.4257</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6238</v>
+        <v>1.6528</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3871</v>
+        <v>0.6965</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2367</v>
+        <v>0.9562</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.761</v>
+        <v>2.9968</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9695</v>
+        <v>1.5637</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2084</v>
+        <v>1.433</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3576</v>
+        <v>3.3732</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4055</v>
+        <v>0.8451</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0479</v>
+        <v>2.5282</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1434</v>
+        <v>3.1252</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9568</v>
+        <v>0.6303</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1866</v>
+        <v>2.4949</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7858000000000001</v>
+        <v>0.2481</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5513</v>
+        <v>0.2148</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2345</v>
+        <v>0.0333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0159</v>
+        <v>1.2868</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6654</v>
+        <v>0.5571</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3505</v>
+        <v>0.7297</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3263</v>
+        <v>2.443</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2947</v>
+        <v>2.6051</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0316</v>
+        <v>-0.1621</v>
       </c>
       <c r="G5" t="n">
-        <v>3.379</v>
+        <v>1.3619</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8573</v>
+        <v>1.4018</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5216</v>
+        <v>-0.0399</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1543</v>
+        <v>2.1339</v>
       </c>
       <c r="K5" t="n">
-        <v>0.654</v>
+        <v>1.9478</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5002</v>
+        <v>0.1862</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2247</v>
+        <v>-0.772</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2033</v>
+        <v>-0.546</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0214</v>
+        <v>-0.226</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.6957</v>
       </c>
       <c r="T5" t="n">
-        <v>0.248</v>
+        <v>0.3134</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3532</v>
+        <v>0.3823</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8188</v>
+        <v>1.3041</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1174</v>
+        <v>1.5778</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2986</v>
+        <v>-0.2737</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5055</v>
+        <v>1.5018</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6335</v>
+        <v>1.6315</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.128</v>
+        <v>-0.1297</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6441</v>
+        <v>0.6236</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8782</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8842</v>
+        <v>1.3682</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3126</v>
+        <v>0.7965</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5716</v>
+        <v>0.5718</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3505</v>
+        <v>1.1503</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7338</v>
+        <v>0.0963</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3833</v>
+        <v>1.054</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4711</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5871</v>
+        <v>1.0109</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0582</v>
+        <v>-0.3159</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1251</v>
+        <v>-0.2381</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2424</v>
+        <v>0.5516</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1174</v>
+        <v>-0.7896</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5962</v>
+        <v>0.9331</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3446</v>
+        <v>0.4593</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9408</v>
+        <v>0.4738</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1165</v>
+        <v>0.2276</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1039</v>
+        <v>0.3344</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0126</v>
+        <v>-0.1067</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.639</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>X. LOPEZ-AROSTEGUI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0866</v>
+        <v>0.9774</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4657</v>
+        <v>-0.5314</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6209</v>
+        <v>1.5089</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2668</v>
+        <v>3.3835</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8758</v>
+        <v>0.6974</v>
       </c>
       <c r="I8" t="n">
-        <v>2.391</v>
+        <v>2.6861</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7643</v>
+        <v>2.5499</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2397</v>
+        <v>1.1721</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5246</v>
+        <v>1.3778</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.8336</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3639</v>
+        <v>-0.4747</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8663999999999999</v>
+        <v>1.3083</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.722</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0882</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3308</v>
+        <v>0.0161</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2426</v>
+        <v>-0.0077</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. LOPEZ-AROSTEGUI</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9503</v>
+        <v>0.9558</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6276</v>
+        <v>1.553</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5779</v>
+        <v>-0.5972</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3671</v>
+        <v>-0.4533</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6881</v>
+        <v>0.5996</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6789</v>
+        <v>-1.0529</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5583</v>
+        <v>0.1143</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1775</v>
+        <v>0.2413</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3807</v>
+        <v>-0.127</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8088</v>
+        <v>-0.5676</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4894</v>
+        <v>0.3583</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2982</v>
+        <v>-0.9258999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.9488</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6293</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0142</v>
+        <v>1.705</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1028</v>
+        <v>0.9427</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0886</v>
+        <v>0.7623</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5463</v>
+        <v>0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5463</v>
+        <v>1.6342</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5522</v>
+        <v>0.8651</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3713</v>
+        <v>1.7597</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9235</v>
+        <v>-0.8946</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6955</v>
+        <v>1.955</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0101</v>
+        <v>2.9438</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3145</v>
+        <v>-0.9887</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2322</v>
+        <v>1.749</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5541</v>
+        <v>2.2408</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>-0.4917</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9277</v>
+        <v>0.206</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4559</v>
+        <v>0.703</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>-0.497</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3702</v>
+        <v>1.4077</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1391</v>
+        <v>0.6268</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2311</v>
+        <v>0.7809</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-2.9529</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4151</v>
+        <v>0.5582</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4704</v>
+        <v>-0.1584</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0554</v>
+        <v>0.7166</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9453</v>
+        <v>3.2722</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9422</v>
+        <v>0.8814</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9968</v>
+        <v>2.3908</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7634</v>
+        <v>2.7384</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2512</v>
+        <v>1.2271</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4878</v>
+        <v>1.5114</v>
       </c>
       <c r="M11" t="n">
-        <v>0.182</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6909999999999999</v>
+        <v>-0.3457</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.509</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9727</v>
+        <v>0.5623</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3176</v>
+        <v>0.7453</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6551</v>
+        <v>-0.183</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9566</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.3461</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3152</v>
+        <v>0.132</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6468</v>
+        <v>-0.6861</v>
       </c>
       <c r="F12" t="n">
-        <v>0.962</v>
+        <v>0.8181</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8194</v>
+        <v>3.3606</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4113</v>
+        <v>1.0738</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2307</v>
+        <v>2.2868</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2424</v>
+        <v>3.0412</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.2205</v>
+        <v>1.2615</v>
       </c>
       <c r="L12" t="n">
-        <v>2.4629</v>
+        <v>1.7797</v>
       </c>
       <c r="M12" t="n">
-        <v>0.577</v>
+        <v>0.3194</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1908</v>
+        <v>-0.1877</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7678</v>
+        <v>0.5071</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-3.6421</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9475</v>
+        <v>-0.11</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2431</v>
+        <v>0.3017</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2955</v>
+        <v>-0.4118</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7712</v>
+        <v>-0.387</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7712</v>
+        <v>-0.387</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4946</v>
+        <v>-0.3617</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1245</v>
+        <v>-1.2561</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6298</v>
+        <v>0.8944</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3494</v>
+        <v>0.8314</v>
       </c>
       <c r="H13" t="n">
-        <v>1.0677</v>
+        <v>-2.4043</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2817</v>
+        <v>3.2357</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0628</v>
+        <v>0.2266</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2743</v>
+        <v>-2.231</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7885</v>
+        <v>2.4576</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2866</v>
+        <v>0.6048</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2066</v>
+        <v>-0.1733</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4932</v>
+        <v>0.778</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.722</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7365</v>
+        <v>0.2638</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1724</v>
+        <v>0.6571</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5641</v>
+        <v>-0.3932</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3856</v>
+        <v>-0.7739</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.3856</v>
+        <v>-0.7739</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.7789</v>
+        <v>27.1342</v>
       </c>
       <c r="E14" t="n">
-        <v>20.4238</v>
+        <v>20.4598</v>
       </c>
       <c r="F14" t="n">
-        <v>6.355</v>
+        <v>6.674300000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>32.66520000000001</v>
+        <v>32.70800000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>11.2476</v>
+        <v>11.2716</v>
       </c>
       <c r="I14" t="n">
-        <v>21.4177</v>
+        <v>21.4364</v>
       </c>
       <c r="J14" t="n">
-        <v>29.3226</v>
+        <v>29.0811</v>
       </c>
       <c r="K14" t="n">
-        <v>10.4779</v>
+        <v>10.3468</v>
       </c>
       <c r="L14" t="n">
-        <v>18.8443</v>
+        <v>18.7347</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3427</v>
+        <v>3.6269</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7695000000000001</v>
+        <v>0.9248999999999998</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5733</v>
+        <v>2.7019</v>
       </c>
       <c r="P14" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="Q14" t="n">
-        <v>-19.2808</v>
+        <v>-19.3487</v>
       </c>
       <c r="R14" t="n">
-        <v>6.805000000000001</v>
+        <v>6.829</v>
       </c>
       <c r="S14" t="n">
-        <v>8.967400000000001</v>
+        <v>9.339200000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>5.8827</v>
+        <v>6.268400000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>3.0847</v>
+        <v>3.070900000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.3778</v>
+        <v>-2.3932</v>
       </c>
       <c r="W14" t="n">
-        <v>4.499599999999999</v>
+        <v>4.4591</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.8774</v>
+        <v>-6.852199999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.87</v>
+        <v>1.9787</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3878</v>
+        <v>2.9239</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4822</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1365</v>
+        <v>0.2077</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5774</v>
+        <v>-0.7156</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7139</v>
+        <v>0.9233</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8006</v>
+        <v>2.7571</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6887</v>
+        <v>0.4342</v>
       </c>
       <c r="L15" t="n">
-        <v>0.112</v>
+        <v>2.3229</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9371</v>
+        <v>-2.5494</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1113</v>
+        <v>-1.1497</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8258</v>
+        <v>-1.3997</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6455</v>
+        <v>-1.5948</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5606</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0848</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9173</v>
+        <v>1.1242</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3664</v>
+        <v>0.2996</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4492</v>
+        <v>0.8246</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2072</v>
+        <v>-1.1415</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.723</v>
+        <v>0.5637</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9302</v>
+        <v>-1.7052</v>
       </c>
       <c r="J16" t="n">
-        <v>2.786</v>
+        <v>0.7765</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4431</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3428</v>
+        <v>0.1117</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5788</v>
+        <v>-1.918</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1662</v>
+        <v>-0.1011</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4126</v>
+        <v>-1.8169</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.6509</v>
+        <v>0.8999</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2854</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3655</v>
+        <v>0.3964</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.381</v>
+        <v>0.5085</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6957</v>
+        <v>0.6233</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3147</v>
+        <v>-0.1149</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9001</v>
+        <v>-0.1109</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0072</v>
+        <v>-1.9445</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8929</v>
+        <v>1.8336</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7856</v>
+        <v>0.965</v>
       </c>
       <c r="K17" t="n">
-        <v>0.599</v>
+        <v>-0.6657</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1866</v>
+        <v>1.6308</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6857</v>
+        <v>-1.0759</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6062</v>
+        <v>-1.2788</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0795</v>
+        <v>0.2028</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1953</v>
+        <v>-0.9756</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0484</v>
+        <v>-0.3417</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1469</v>
+        <v>-0.6339</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7959</v>
+        <v>0.2292</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6105</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.055</v>
+        <v>0.2928</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2887</v>
+        <v>2.2062</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2337</v>
+        <v>-1.9134</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1101</v>
+        <v>-1.8913</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9466</v>
+        <v>-1.0053</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8365</v>
+        <v>-0.886</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9843</v>
+        <v>0.7755</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6549</v>
+        <v>0.5893</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6392</v>
+        <v>0.1862</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0944</v>
+        <v>-2.6668</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2917</v>
+        <v>-1.5946</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1973</v>
+        <v>-1.0722</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4209</v>
+        <v>-1.2939</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6956</v>
+        <v>-0.5206</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.7733</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2249</v>
+        <v>2.7951</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3662</v>
+        <v>-0.3878</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6854</v>
+        <v>1.206</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0516</v>
+        <v>-1.5938</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4456</v>
+        <v>-2.8102</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6651</v>
+        <v>2.0549</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.1107</v>
+        <v>-4.8651</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2098</v>
+        <v>1.2287</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9177999999999999</v>
+        <v>3.0467</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1276</v>
+        <v>-1.818</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.2357</v>
+        <v>-4.0389</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2526</v>
+        <v>-0.9918</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.9831</v>
+        <v>-3.0471</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8129999999999999</v>
+        <v>-0.6867</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8953</v>
+        <v>-0.4002</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0823</v>
+        <v>-0.2865</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3214</v>
+        <v>2.8814</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.8814</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1836</v>
+        <v>-0.8408</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0457</v>
+        <v>-0.0365</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2293</v>
+        <v>-0.8043</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7849</v>
+        <v>-2.446</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0797</v>
+        <v>0.669</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.8646</v>
+        <v>-3.115</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2866</v>
+        <v>-0.2266</v>
       </c>
       <c r="K20" t="n">
-        <v>3.0886</v>
+        <v>0.9136</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.802</v>
+        <v>-1.1401</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.0715</v>
+        <v>-2.2194</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0089</v>
+        <v>-0.2446</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.0626</v>
+        <v>-1.9749</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.518</v>
+        <v>0.3273</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6381</v>
+        <v>0.1901</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8798</v>
+        <v>0.1372</v>
       </c>
       <c r="V20" t="n">
-        <v>2.8924</v>
+        <v>-0.3155</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8924</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8558</v>
+        <v>-1.5157</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1013</v>
+        <v>0.1353</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7545</v>
+        <v>-1.651</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7048</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.153</v>
+        <v>-0.1495</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5517</v>
+        <v>-0.5496</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0893</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.794</v>
+        <v>-0.7881</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2852</v>
+        <v>0.0452</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1905</v>
+        <v>0.0463</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.337</v>
+        <v>-1.8751</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.069</v>
+        <v>-1.8402</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2681</v>
+        <v>-0.0348</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7909</v>
+        <v>-0.781</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3161</v>
+        <v>-1.31</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5251</v>
+        <v>0.529</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6051</v>
+        <v>-0.609</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1858</v>
+        <v>-0.172</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3193</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3297</v>
+        <v>-0.0931</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9896</v>
+        <v>-0.7733</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0199</v>
+        <v>-3.7998</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8808</v>
+        <v>-3.0363</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1391</v>
+        <v>-0.7635</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.8399</v>
+        <v>-4.859</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6753</v>
+        <v>-2.6713</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1646</v>
+        <v>-2.1878</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7992</v>
+        <v>-2.8384</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3995</v>
+        <v>-1.4069</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3997</v>
+        <v>-1.4314</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0407</v>
+        <v>-2.0207</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6732</v>
+        <v>-0.4462</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1979</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5916</v>
+        <v>-0.2483</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5142</v>
+        <v>-6.3278</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5556</v>
+        <v>-3.4523</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9585</v>
+        <v>-2.8755</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.7762</v>
+        <v>-4.7761</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.8065</v>
+        <v>-2.8115</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9698</v>
+        <v>-1.9646</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.9296</v>
+        <v>-2.9434</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.2552</v>
+        <v>-2.2655</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8467</v>
+        <v>-1.8326</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5526</v>
+        <v>-0.3728</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>-0.2812</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1534</v>
+        <v>-0.0915</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8229</v>
+        <v>-6.4335</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1981</v>
+        <v>-3.2171</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.6248</v>
+        <v>-3.2164</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.4933</v>
+        <v>-7.4902</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.1832</v>
+        <v>-3.1823</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.3101</v>
+        <v>-4.3079</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.5418</v>
+        <v>-2.5615</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.2379</v>
+        <v>-2.2483</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.9515</v>
+        <v>-4.9287</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.0062</v>
+        <v>-3.9946</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9835</v>
+        <v>-0.6066</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4294</v>
+        <v>-0.428</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5541</v>
+        <v>-0.1786</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.9024</v>
+        <v>-7.1405</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.02</v>
+        <v>-2.4861</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.8825</v>
+        <v>-4.6544</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.89</v>
+        <v>-5.9103</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7588</v>
+        <v>-0.7692</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.1312</v>
+        <v>-5.1411</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9895</v>
+        <v>-1.0397</v>
       </c>
       <c r="K26" t="n">
-        <v>0.706</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.6955</v>
+        <v>-1.7217</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.9006</v>
+        <v>-4.8706</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.4357</v>
+        <v>-3.4194</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.8271</v>
+        <v>-1.0513</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.4426</v>
+        <v>-0.853</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3844</v>
+        <v>-0.1983</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-26.7787</v>
+        <v>-24.4168</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.3551</v>
+        <v>-6.674200000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-20.4238</v>
+        <v>-17.7425</v>
       </c>
       <c r="G27" t="n">
-        <v>-32.6651</v>
+        <v>-32.7079</v>
       </c>
       <c r="H27" t="n">
-        <v>-11.2475</v>
+        <v>-11.2716</v>
       </c>
       <c r="I27" t="n">
-        <v>-21.4177</v>
+        <v>-21.4364</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.3426</v>
+        <v>-3.6269</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7693999999999992</v>
+        <v>-0.9247999999999997</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.5732</v>
+        <v>-2.7018</v>
       </c>
       <c r="M27" t="n">
-        <v>-29.3225</v>
+        <v>-29.0811</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.4781</v>
+        <v>-10.3465</v>
       </c>
       <c r="O27" t="n">
-        <v>-18.8444</v>
+        <v>-18.7344</v>
       </c>
       <c r="P27" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="Q27" t="n">
-        <v>-6.805</v>
+        <v>-6.8289</v>
       </c>
       <c r="R27" t="n">
-        <v>19.2808</v>
+        <v>19.3486</v>
       </c>
       <c r="S27" t="n">
-        <v>-8.967500000000001</v>
+        <v>-6.6219</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.0846</v>
+        <v>-3.0709</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.8828</v>
+        <v>-3.5509</v>
       </c>
       <c r="V27" t="n">
-        <v>2.378</v>
+        <v>2.3932</v>
       </c>
       <c r="W27" t="n">
-        <v>6.8774</v>
+        <v>6.8523</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.499499999999999</v>
+        <v>-4.459099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104644_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104644_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-6.852199999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104644_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.459099999999999</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
